--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260804.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260804.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.21%</t>
+          <t>11.23%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.66%</t>
+          <t>10.65%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.91%</t>
+          <t>7.95%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.77%</t>
+          <t>7.88%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.53%</t>
+          <t>5.50%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.16%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.61%</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>HUBB US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>安柏</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>58,759</t>
+          <t>19,279</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>HUBB US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>安柏</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,279</t>
+          <t>58,759</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1012,51 +1012,51 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>51,110</t>
+          <t>49,960</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>49,960</t>
+          <t>51,110</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1107,88 +1107,88 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>22,158</t>
+          <t>30,345</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>30,345</t>
+          <t>94,763</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>94,763</t>
+          <t>22,158</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>27,469</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1232,51 +1232,51 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>20,609</t>
+          <t>27,469</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>20,609</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1298,24 +1298,24 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>145,545</t>
+          <t>13,252</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>13,252</t>
+          <t>145,545</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>202609ESU6</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10,646</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,132 +1393,132 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>CMS US</t>
+          <t>202609ESU6</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>CMS能源</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>30,591</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>CMS US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>CMS能源</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>10,646</t>
+          <t>30,591</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>13,424</t>
+          <t>25,681</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>25,681</t>
+          <t>43,383</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>43,383</t>
+          <t>16,127</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>16,127</t>
+          <t>13,424</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>97,457,406</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
